--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512401_1ºE1ºOFINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512401_1ºE1ºOFINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.376099999999999</v>
+        <v>7.9371</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9935</v>
+        <v>5.5334</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3826</v>
+        <v>2.4038</v>
       </c>
       <c r="G2" t="n">
-        <v>5.9112</v>
+        <v>5.9875</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9576</v>
+        <v>2.0134</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9536</v>
+        <v>3.9741</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0725</v>
+        <v>5.2055</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5121</v>
+        <v>1.5968</v>
       </c>
       <c r="L2" t="n">
-        <v>3.5604</v>
+        <v>3.6087</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8387</v>
+        <v>0.7819</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4455</v>
+        <v>0.4166</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3932</v>
+        <v>0.3654</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.2776</v>
+        <v>-3.2392</v>
       </c>
       <c r="R2" t="n">
-        <v>2.8679</v>
+        <v>2.8343</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2702</v>
+        <v>0.7385</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2472</v>
+        <v>0.5915</v>
       </c>
       <c r="U2" t="n">
-        <v>0.023</v>
+        <v>0.1469</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6044</v>
+        <v>1.6161</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9515</v>
+        <v>2.9755</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3471</v>
+        <v>-1.3594</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4961</v>
+        <v>5.6167</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7898</v>
+        <v>4.227</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7063</v>
+        <v>1.3897</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7406</v>
+        <v>2.7812</v>
       </c>
       <c r="H3" t="n">
-        <v>3.273</v>
+        <v>3.3186</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5324</v>
+        <v>-0.5374</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2219</v>
+        <v>3.3278</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2178</v>
+        <v>3.2971</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004</v>
+        <v>0.0307</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4812</v>
+        <v>-0.5467</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0552</v>
+        <v>0.0215</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5364</v>
+        <v>-0.5682</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R3" t="n">
-        <v>3.2776</v>
+        <v>3.2392</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8735</v>
+        <v>0.9802</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6164</v>
+        <v>0.9237</v>
       </c>
       <c r="U3" t="n">
-        <v>0.257</v>
+        <v>0.0565</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1665</v>
+        <v>-0.1692</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3471</v>
+        <v>-1.3594</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5522</v>
+        <v>5.0047</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8553</v>
+        <v>3.2181</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6969</v>
+        <v>1.7866</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7932</v>
+        <v>1.7815</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1984</v>
+        <v>1.1866</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5948</v>
+        <v>0.5949</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0499</v>
+        <v>3.0971</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7564</v>
+        <v>1.7779</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2935</v>
+        <v>1.3192</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2567</v>
+        <v>-1.3156</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5913</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6987</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8679</v>
+        <v>2.8343</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6657999999999999</v>
+        <v>1.1662</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5504</v>
+        <v>0.8338</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1154</v>
+        <v>0.3324</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4544</v>
+        <v>0.4374</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4841</v>
+        <v>0.5019</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0297</v>
+        <v>-0.0645</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8506</v>
+        <v>4.2815</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9368</v>
+        <v>3.2302</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9139</v>
+        <v>1.0514</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9612</v>
+        <v>2.9917</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.984</v>
+        <v>-0.9881</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9452</v>
+        <v>3.9798</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0831</v>
+        <v>3.1525</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3982</v>
+        <v>-0.3767</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4814</v>
+        <v>3.5292</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1219</v>
+        <v>-0.1608</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5857</v>
+        <v>-0.6115</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4639</v>
+        <v>0.4507</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9926</v>
+        <v>-0.5655</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1464</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.6431</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1665</v>
+        <v>-0.1692</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1665</v>
+        <v>-0.1692</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2589</v>
+        <v>3.5414</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5716</v>
+        <v>1.6706</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6873</v>
+        <v>1.8708</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0114</v>
+        <v>1.0019</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4851</v>
+        <v>0.4937</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5263</v>
+        <v>0.5081</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3575</v>
+        <v>0.3749</v>
       </c>
       <c r="K6" t="n">
-        <v>0.318</v>
+        <v>0.3352</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0395</v>
+        <v>0.0398</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6539</v>
+        <v>0.6269</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1671</v>
+        <v>0.1586</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4868</v>
+        <v>0.4684</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.449</v>
+        <v>-0.1488</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2383</v>
+        <v>0.3079</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6873</v>
+        <v>-0.4567</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8771</v>
+        <v>1.8785</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7807</v>
+        <v>2.1553</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5058</v>
+        <v>0.4582</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2749</v>
+        <v>1.6971</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1219</v>
+        <v>1.1183</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1904</v>
+        <v>1.2051</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0868</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5775</v>
+        <v>0.6111</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1185</v>
+        <v>0.1193</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4258</v>
+        <v>0.388</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6129</v>
+        <v>0.594</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1871</v>
+        <v>-0.206</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.6388</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4511</v>
+        <v>0.7896</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5816</v>
+        <v>0.0612</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8465</v>
+        <v>1.867</v>
       </c>
       <c r="W7" t="n">
-        <v>2.013</v>
+        <v>2.0362</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1665</v>
+        <v>-0.1692</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1276</v>
+        <v>1.076</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2248</v>
+        <v>-0.9397</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3524</v>
+        <v>2.0157</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1096</v>
+        <v>0.1259</v>
       </c>
       <c r="H8" t="n">
-        <v>1.946</v>
+        <v>1.9752</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8364</v>
+        <v>-1.8493</v>
       </c>
       <c r="J8" t="n">
-        <v>0.507</v>
+        <v>0.5745</v>
       </c>
       <c r="K8" t="n">
-        <v>1.807</v>
+        <v>1.8556</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3</v>
+        <v>-1.2812</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3974</v>
+        <v>-0.4486</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1391</v>
+        <v>0.1196</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5364</v>
+        <v>-0.5682</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4582</v>
+        <v>2.4294</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4289</v>
+        <v>0.4967</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7205</v>
+        <v>0.4618</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2916</v>
+        <v>0.0349</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3738</v>
+        <v>-0.283</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0585</v>
+        <v>0.1631</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4324</v>
+        <v>-0.446</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1973</v>
+        <v>-0.1999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0585</v>
+        <v>0.0593</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2558</v>
+        <v>-0.2591</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0585</v>
+        <v>0.0593</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0585</v>
+        <v>0.0593</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2558</v>
+        <v>-0.2591</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2558</v>
+        <v>-0.2591</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1394</v>
+        <v>-0.0346</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.1038</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1394</v>
+        <v>-0.1384</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7869</v>
+        <v>-2.3098</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3485</v>
+        <v>-2.9329</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5617</v>
+        <v>0.6231</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4612</v>
+        <v>-1.4643</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6947</v>
+        <v>-0.6935</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8741</v>
+        <v>-1.8582</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5992</v>
+        <v>-0.5933</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.275</v>
+        <v>-1.2649</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4129</v>
+        <v>0.394</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1674</v>
+        <v>-0.1774</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5803</v>
+        <v>0.5714</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5931</v>
+        <v>-0.0935</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4501</v>
+        <v>-0.0624</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.143</v>
+        <v>-0.0311</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3471</v>
+        <v>-1.3594</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3471</v>
+        <v>-1.3594</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0196</v>
+        <v>-3.1161</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9169</v>
+        <v>-1.9223</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1027</v>
+        <v>-1.1938</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2574</v>
+        <v>-2.2585</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6913</v>
+        <v>-0.6918</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5661</v>
+        <v>-1.5667</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2619</v>
+        <v>-1.2422</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5797</v>
+        <v>-0.5736</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6822</v>
+        <v>-0.6686</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9954</v>
+        <v>-1.0164</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1116</v>
+        <v>-0.1183</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8838</v>
+        <v>-0.8981</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0458</v>
+        <v>-0.0238</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3693</v>
+        <v>0.3321</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3234</v>
+        <v>-0.3559</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="12">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>23.2619</v>
+        <v>23.9038</v>
       </c>
       <c r="E12" t="n">
-        <v>11.2211</v>
+        <v>12.7057</v>
       </c>
       <c r="F12" t="n">
-        <v>12.0409</v>
+        <v>11.1984</v>
       </c>
       <c r="G12" t="n">
-        <v>11.7332</v>
+        <v>11.8653</v>
       </c>
       <c r="H12" t="n">
-        <v>7.6671</v>
+        <v>7.8013</v>
       </c>
       <c r="I12" t="n">
-        <v>4.065999999999999</v>
+        <v>4.0641</v>
       </c>
       <c r="J12" t="n">
-        <v>12.9105</v>
+        <v>13.4215</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6702</v>
+        <v>7.989400000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>5.2401</v>
+        <v>5.432200000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1771</v>
+        <v>-1.5564</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.002899999999999875</v>
+        <v>-0.1882000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.174</v>
+        <v>-1.368</v>
       </c>
       <c r="P12" t="n">
-        <v>6.145300000000001</v>
+        <v>6.073700000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.315</v>
+        <v>-13.1595</v>
       </c>
       <c r="R12" t="n">
-        <v>19.4606</v>
+        <v>19.2329</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7034</v>
+        <v>3.305</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5741</v>
+        <v>4.2982</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8708000000000001</v>
+        <v>-0.9933000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>2.679600000000001</v>
+        <v>2.660099999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>8.0519</v>
+        <v>8.1449</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.3723</v>
+        <v>-5.4848</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. SCHUTTE</t>
+          <t>F. BELLO MOURE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.15</v>
+        <v>-0.1852</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4956</v>
+        <v>-0.8064</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3456</v>
+        <v>0.6212</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6554</v>
+        <v>-0.4361</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.0784</v>
       </c>
       <c r="I13" t="n">
+        <v>-0.3578</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9587</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6433</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-1.3949</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.3938</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-1.0011</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.2025</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-2.0245</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.8221</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2025</v>
+      </c>
+      <c r="T13" t="n">
         <v>0.008399999999999999</v>
       </c>
-      <c r="J13" t="n">
-        <v>1.4606</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.5911999999999999</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.8693</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-2.116</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-1.255</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-0.8609</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.4097</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-2.0485</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.4582</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.6378</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.903</v>
-      </c>
       <c r="U13" t="n">
-        <v>-0.2651</v>
+        <v>0.194</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1806</v>
+        <v>0.2509</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4227</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. BELLO MOURE</t>
+          <t>K. SCHUTTE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1779</v>
+        <v>-0.5134</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8932</v>
+        <v>1.0463</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7153</v>
+        <v>-1.5597</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.42</v>
+        <v>-0.6963</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0643</v>
+        <v>-0.6905</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3556</v>
+        <v>-0.0058</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9203</v>
+        <v>1.4863</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2985</v>
+        <v>0.6117</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6218</v>
+        <v>0.8746</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3402</v>
+        <v>-2.1826</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3628</v>
+        <v>-1.3022</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9774</v>
+        <v>-0.8804</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2048</v>
+        <v>0.4049</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8436</v>
+        <v>2.4294</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2048</v>
+        <v>0.029</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.007</v>
+        <v>0.3943</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2119</v>
+        <v>-0.3653</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2421</v>
+        <v>1.1902</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. SAGNIA</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8146</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1724</v>
+        <v>0.6843</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9869</v>
+        <v>-1.4056</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7759</v>
+        <v>1.6321</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2872</v>
+        <v>-1.3437</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4887</v>
+        <v>2.9758</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0195</v>
+        <v>3.3202</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0195</v>
+        <v>0.156</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.1641</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7954</v>
+        <v>-1.6881</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3068</v>
+        <v>-1.4998</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4887</v>
+        <v>-0.1883</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.0242</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.2291</v>
+        <v>-4.049</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2048</v>
+        <v>2.0245</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9856</v>
+        <v>-0.924</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1399</v>
+        <v>-0.3722</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1543</v>
+        <v>-0.5518</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.5951</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2421</v>
+        <v>1.7853</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2421</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>N. SAGNIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.303</v>
+        <v>-1.3275</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2213</v>
+        <v>-0.5323</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5243</v>
+        <v>-0.7952</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6368</v>
+        <v>-0.7966</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3353</v>
+        <v>-0.2961</v>
       </c>
       <c r="I16" t="n">
-        <v>2.972</v>
+        <v>-0.5006</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2511</v>
+        <v>0.0198</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1149</v>
+        <v>0.0198</v>
       </c>
       <c r="L16" t="n">
-        <v>3.1362</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6144</v>
+        <v>-0.8164</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4502</v>
+        <v>-0.3158</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1642</v>
+        <v>-0.5006</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.0485</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.097</v>
+        <v>-1.2147</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0485</v>
+        <v>0.2025</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4816</v>
+        <v>0.4814</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7038</v>
+        <v>0.4117</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7778</v>
+        <v>0.0697</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5903</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7709</v>
+        <v>0.2509</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1806</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.705</v>
+        <v>-1.7684</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3942</v>
+        <v>-1.1178</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3107</v>
+        <v>-0.6506</v>
       </c>
       <c r="G17" t="n">
-        <v>0.538</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2264</v>
+        <v>1.2256</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6884</v>
+        <v>-0.6979</v>
       </c>
       <c r="J17" t="n">
-        <v>0.358</v>
+        <v>0.3752</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9758</v>
+        <v>0.9877</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6177</v>
+        <v>-0.6126</v>
       </c>
       <c r="M17" t="n">
-        <v>0.18</v>
+        <v>0.1526</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2507</v>
+        <v>0.2379</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0706</v>
+        <v>-0.0853</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3548</v>
+        <v>0.283</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3108</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6656</v>
+        <v>0.3748</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.9833</v>
+        <v>-1.9718</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.2124</v>
+        <v>-0.1865</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7709</v>
+        <v>-1.7853</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BLACK</t>
+          <t>P. SANCHEZ INFANTES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6185</v>
+        <v>-2.1471</v>
       </c>
       <c r="E18" t="n">
-        <v>1.259</v>
+        <v>-2.1746</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.8775</v>
+        <v>0.0275</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4301</v>
+        <v>-4.6741</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7731</v>
+        <v>-1.8779</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3431</v>
+        <v>-2.7962</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2204</v>
+        <v>-3.7572</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3787</v>
+        <v>-1.7207</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5991</v>
+        <v>-2.0365</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6505</v>
+        <v>-0.9169</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3944</v>
+        <v>-0.1572</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2561</v>
+        <v>-0.7597</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4097</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0242</v>
+        <v>-1.2147</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4339</v>
+        <v>1.0123</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1728</v>
+        <v>0.0982</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8207</v>
+        <v>0.1659</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.648</v>
+        <v>-0.0678</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.7709</v>
+        <v>2.6313</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2421</v>
+        <v>2.6313</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SANCHEZ INFANTES</t>
+          <t>J. BLACK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6346</v>
+        <v>-2.9664</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7835</v>
+        <v>0.7319</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1489</v>
+        <v>-3.6983</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.6739</v>
+        <v>-1.4311</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8786</v>
+        <v>-1.7976</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.7953</v>
+        <v>0.3665</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.7898</v>
+        <v>1.2875</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.739</v>
+        <v>-0.3569</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0508</v>
+        <v>1.6444</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8841</v>
+        <v>-2.7186</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1396</v>
+        <v>-1.4406</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-1.278</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2048</v>
+        <v>0.4049</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.2291</v>
+        <v>-1.0123</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0242</v>
+        <v>1.4172</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3591</v>
+        <v>-0.1549</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3679</v>
+        <v>0.2057</v>
       </c>
       <c r="U19" t="n">
-        <v>0.008800000000000001</v>
+        <v>-0.3606</v>
       </c>
       <c r="V19" t="n">
-        <v>2.6033</v>
+        <v>-1.7853</v>
       </c>
       <c r="W19" t="n">
-        <v>2.6033</v>
+        <v>0.2509</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.0362</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2791</v>
+        <v>-3.2936</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7564</v>
+        <v>-1.5516</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5227</v>
+        <v>-1.742</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4781</v>
+        <v>-2.5062</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7226</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7554</v>
+        <v>-1.7376</v>
       </c>
       <c r="J20" t="n">
-        <v>0.094</v>
+        <v>0.1544</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0343</v>
+        <v>1.047</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9403</v>
+        <v>-0.8925999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5721</v>
+        <v>-2.6606</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7569</v>
+        <v>-1.8156</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8151</v>
+        <v>-0.845</v>
       </c>
       <c r="P20" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8867</v>
+        <v>-0.8604000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1296</v>
+        <v>-0.0054</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7571</v>
+        <v>-0.855</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9385</v>
+        <v>-0.9393</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5212</v>
+        <v>-3.9776</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6398</v>
+        <v>-3.1688</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8814</v>
+        <v>-0.8088</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0264</v>
+        <v>-2.0143</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2069</v>
+        <v>-1.2059</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8195</v>
+        <v>-0.8085</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.2393</v>
+        <v>-2.2083</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.374</v>
+        <v>-1.3644</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8653</v>
+        <v>-0.8439</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2129</v>
+        <v>0.194</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1671</v>
+        <v>0.1586</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0458</v>
+        <v>0.0354</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6997</v>
+        <v>-0.1657</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1714</v>
+        <v>0.2542</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5283</v>
+        <v>-0.42</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3582</v>
+        <v>-5.6711</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.722</v>
+        <v>-4.3094</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6361</v>
+        <v>-1.3617</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4483</v>
+        <v>-1.4703</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9617</v>
+        <v>-0.9683</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4866</v>
+        <v>-0.502</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1178</v>
+        <v>-0.0803</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4604</v>
+        <v>0.4925</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5782</v>
+        <v>-0.5728</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3305</v>
+        <v>-1.39</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4222</v>
+        <v>-1.4608</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0916</v>
+        <v>0.0708</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.2776</v>
+        <v>-3.2392</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.3018</v>
+        <v>-4.2515</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6322</v>
+        <v>-0.9616</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3024</v>
+        <v>0.0223</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.3298</v>
+        <v>-0.984</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-23.2621</v>
+        <v>-22.5716</v>
       </c>
       <c r="E23" t="n">
-        <v>-12.0408</v>
+        <v>-11.1984</v>
       </c>
       <c r="F23" t="n">
-        <v>-11.221</v>
+        <v>-11.3732</v>
       </c>
       <c r="G23" t="n">
-        <v>-11.7333</v>
+        <v>-11.8652</v>
       </c>
       <c r="H23" t="n">
-        <v>-7.6671</v>
+        <v>-7.8014</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.066</v>
+        <v>-4.0641</v>
       </c>
       <c r="J23" t="n">
-        <v>1.177</v>
+        <v>1.5563</v>
       </c>
       <c r="K23" t="n">
-        <v>0.002899999999999736</v>
+        <v>0.1881</v>
       </c>
       <c r="L23" t="n">
-        <v>1.174099999999999</v>
+        <v>1.368</v>
       </c>
       <c r="M23" t="n">
-        <v>-12.9103</v>
+        <v>-13.4215</v>
       </c>
       <c r="N23" t="n">
-        <v>-7.6701</v>
+        <v>-7.989300000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>-5.240100000000001</v>
+        <v>-5.432200000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-6.145300000000001</v>
+        <v>-6.073700000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>-19.4606</v>
+        <v>-19.2329</v>
       </c>
       <c r="R23" t="n">
-        <v>13.3149</v>
+        <v>13.1596</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.7035</v>
+        <v>-1.9725</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8707</v>
+        <v>0.9931</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.5741</v>
+        <v>-2.966</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.6797</v>
+        <v>-2.6602</v>
       </c>
       <c r="W23" t="n">
-        <v>5.372199999999999</v>
+        <v>5.4847</v>
       </c>
       <c r="X23" t="n">
-        <v>-8.052</v>
+        <v>-8.1448</v>
       </c>
     </row>
   </sheetData>
